--- a/artfynd/A 15280-2025 artfynd.xlsx
+++ b/artfynd/A 15280-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123737290</v>
+        <v>123737262</v>
       </c>
       <c r="B2" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573157</v>
+        <v>573214</v>
       </c>
       <c r="R2" t="n">
-        <v>6418382</v>
+        <v>6418328</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123737360</v>
+        <v>123737248</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>57860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,12 +827,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573186</v>
+        <v>573300</v>
       </c>
       <c r="R3" t="n">
-        <v>6418398</v>
+        <v>6418290</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123737397</v>
+        <v>123737290</v>
       </c>
       <c r="B4" t="n">
-        <v>95167</v>
+        <v>98502</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,42 +915,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 15280. Stenserum, Sm</t>
+          <t>A 15280, Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573206</v>
+        <v>573157</v>
       </c>
       <c r="R4" t="n">
-        <v>6418383</v>
+        <v>6418382</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123737248</v>
+        <v>123737397</v>
       </c>
       <c r="B5" t="n">
-        <v>57857</v>
+        <v>95173</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,49 +1034,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 15280, Stenserum, Sm</t>
+          <t>A 15280. Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573300</v>
+        <v>573206</v>
       </c>
       <c r="R5" t="n">
-        <v>6418290</v>
+        <v>6418383</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1125,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123737422</v>
+        <v>123737360</v>
       </c>
       <c r="B6" t="n">
-        <v>105502</v>
+        <v>90988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,35 +1137,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573334</v>
+        <v>573186</v>
       </c>
       <c r="R6" t="n">
-        <v>6418407</v>
+        <v>6418398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1239,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123737262</v>
+        <v>123737422</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
+        <v>105518</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,39 +1251,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573214</v>
+        <v>573334</v>
       </c>
       <c r="R7" t="n">
-        <v>6418328</v>
+        <v>6418407</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,6 +1331,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15280-2025 artfynd.xlsx
+++ b/artfynd/A 15280-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123737262</v>
+        <v>123737422</v>
       </c>
       <c r="B2" t="n">
-        <v>57506</v>
+        <v>105520</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573214</v>
+        <v>573334</v>
       </c>
       <c r="R2" t="n">
-        <v>6418328</v>
+        <v>6418407</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +767,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123737248</v>
+        <v>123737360</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,13 +824,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -841,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573300</v>
+        <v>573186</v>
       </c>
       <c r="R3" t="n">
-        <v>6418290</v>
+        <v>6418398</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123737290</v>
+        <v>123737262</v>
       </c>
       <c r="B4" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +912,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -955,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573157</v>
+        <v>573214</v>
       </c>
       <c r="R4" t="n">
-        <v>6418382</v>
+        <v>6418328</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1021,7 +1017,7 @@
         <v>123737397</v>
       </c>
       <c r="B5" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1125,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123737360</v>
+        <v>123737248</v>
       </c>
       <c r="B6" t="n">
-        <v>90988</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,12 +1159,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1176,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573186</v>
+        <v>573300</v>
       </c>
       <c r="R6" t="n">
-        <v>6418398</v>
+        <v>6418290</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,7 +1217,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123737422</v>
+        <v>123737290</v>
       </c>
       <c r="B7" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,28 +1247,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573334</v>
+        <v>573157</v>
       </c>
       <c r="R7" t="n">
-        <v>6418407</v>
+        <v>6418382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 15280-2025 artfynd.xlsx
+++ b/artfynd/A 15280-2025 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123737397</v>
+        <v>123737248</v>
       </c>
       <c r="B5" t="n">
-        <v>95175</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,41 +1030,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 15280. Stenserum, Sm</t>
+          <t>A 15280, Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573206</v>
+        <v>573300</v>
       </c>
       <c r="R5" t="n">
-        <v>6418383</v>
+        <v>6418290</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1110,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123737248</v>
+        <v>123737397</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>95175</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,49 +1144,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 15280, Stenserum, Sm</t>
+          <t>A 15280. Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573300</v>
+        <v>573206</v>
       </c>
       <c r="R6" t="n">
-        <v>6418290</v>
+        <v>6418383</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,6 +1216,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15280-2025 artfynd.xlsx
+++ b/artfynd/A 15280-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123737422</v>
+        <v>123737290</v>
       </c>
       <c r="B2" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -723,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573334</v>
+        <v>573157</v>
       </c>
       <c r="R2" t="n">
-        <v>6418407</v>
+        <v>6418382</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123737360</v>
+        <v>123737422</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>105095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573186</v>
+        <v>573334</v>
       </c>
       <c r="R3" t="n">
-        <v>6418398</v>
+        <v>6418407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123737262</v>
+        <v>123737248</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,20 +913,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -942,7 +943,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -952,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573214</v>
+        <v>573300</v>
       </c>
       <c r="R4" t="n">
-        <v>6418328</v>
+        <v>6418290</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123737248</v>
+        <v>123737360</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,13 +1053,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573300</v>
+        <v>573186</v>
       </c>
       <c r="R5" t="n">
-        <v>6418290</v>
+        <v>6418398</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,6 +1110,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1131,7 +1132,7 @@
         <v>123737397</v>
       </c>
       <c r="B6" t="n">
-        <v>95175</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123737290</v>
+        <v>123737262</v>
       </c>
       <c r="B7" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,39 +1248,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,13 +1288,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573157</v>
+        <v>573214</v>
       </c>
       <c r="R7" t="n">
-        <v>6418382</v>
+        <v>6418328</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1332,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15280-2025 artfynd.xlsx
+++ b/artfynd/A 15280-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123737290</v>
+        <v>123737248</v>
       </c>
       <c r="B2" t="n">
-        <v>98079</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573157</v>
+        <v>573300</v>
       </c>
       <c r="R2" t="n">
-        <v>6418382</v>
+        <v>6418290</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +771,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123737422</v>
+        <v>123737397</v>
       </c>
       <c r="B3" t="n">
-        <v>105095</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,42 +805,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 15280, Stenserum, Sm</t>
+          <t>A 15280. Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573334</v>
+        <v>573206</v>
       </c>
       <c r="R3" t="n">
-        <v>6418407</v>
+        <v>6418383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123737248</v>
+        <v>123737290</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,39 +908,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -953,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573300</v>
+        <v>573157</v>
       </c>
       <c r="R4" t="n">
-        <v>6418290</v>
+        <v>6418382</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,6 +992,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123737360</v>
+        <v>123737262</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1053,12 +1049,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1066,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573186</v>
+        <v>573214</v>
       </c>
       <c r="R5" t="n">
-        <v>6418398</v>
+        <v>6418328</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1107,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123737397</v>
+        <v>123737422</v>
       </c>
       <c r="B6" t="n">
-        <v>95683</v>
+        <v>105095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,38 +1141,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 15280. Stenserum, Sm</t>
+          <t>A 15280, Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573206</v>
+        <v>573334</v>
       </c>
       <c r="R6" t="n">
-        <v>6418383</v>
+        <v>6418407</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123737262</v>
+        <v>123737360</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,21 +1252,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,13 +1274,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573214</v>
+        <v>573186</v>
       </c>
       <c r="R7" t="n">
-        <v>6418328</v>
+        <v>6418398</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,6 +1331,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15280-2025 artfynd.xlsx
+++ b/artfynd/A 15280-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123737248</v>
+        <v>123737262</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573300</v>
+        <v>573214</v>
       </c>
       <c r="R2" t="n">
-        <v>6418290</v>
+        <v>6418328</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123737397</v>
+        <v>123737422</v>
       </c>
       <c r="B3" t="n">
-        <v>95683</v>
+        <v>105095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,38 +805,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 15280. Stenserum, Sm</t>
+          <t>A 15280, Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573206</v>
+        <v>573334</v>
       </c>
       <c r="R3" t="n">
-        <v>6418383</v>
+        <v>6418407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123737290</v>
+        <v>123737397</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>95683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,50 +912,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 15280, Stenserum, Sm</t>
+          <t>A 15280. Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573157</v>
+        <v>573206</v>
       </c>
       <c r="R4" t="n">
-        <v>6418382</v>
+        <v>6418383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123737262</v>
+        <v>123737248</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,20 +1019,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1053,7 +1049,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1063,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573214</v>
+        <v>573300</v>
       </c>
       <c r="R5" t="n">
-        <v>6418328</v>
+        <v>6418290</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1125,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123737422</v>
+        <v>123737360</v>
       </c>
       <c r="B6" t="n">
-        <v>105095</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,35 +1133,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573334</v>
+        <v>573186</v>
       </c>
       <c r="R6" t="n">
-        <v>6418407</v>
+        <v>6418398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123737360</v>
+        <v>123737290</v>
       </c>
       <c r="B7" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,38 +1247,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573186</v>
+        <v>573157</v>
       </c>
       <c r="R7" t="n">
-        <v>6418398</v>
+        <v>6418382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 15280-2025 artfynd.xlsx
+++ b/artfynd/A 15280-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123737262</v>
+        <v>123737248</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573214</v>
+        <v>573300</v>
       </c>
       <c r="R2" t="n">
-        <v>6418328</v>
+        <v>6418290</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123737422</v>
+        <v>123737290</v>
       </c>
       <c r="B3" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,28 +801,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573334</v>
+        <v>573157</v>
       </c>
       <c r="R3" t="n">
-        <v>6418407</v>
+        <v>6418382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123737397</v>
+        <v>123737422</v>
       </c>
       <c r="B4" t="n">
-        <v>95683</v>
+        <v>105095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +920,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 15280. Stenserum, Sm</t>
+          <t>A 15280, Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573206</v>
+        <v>573334</v>
       </c>
       <c r="R4" t="n">
-        <v>6418383</v>
+        <v>6418407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123737248</v>
+        <v>123737360</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,25 +1027,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1045,13 +1053,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,13 +1066,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573300</v>
+        <v>573186</v>
       </c>
       <c r="R5" t="n">
-        <v>6418290</v>
+        <v>6418398</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,6 +1110,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123737360</v>
+        <v>123737397</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>95683</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,49 +1141,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 15280, Stenserum, Sm</t>
+          <t>A 15280. Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573186</v>
+        <v>573206</v>
       </c>
       <c r="R6" t="n">
-        <v>6418398</v>
+        <v>6418383</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123737290</v>
+        <v>123737262</v>
       </c>
       <c r="B7" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,39 +1248,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,13 +1288,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573157</v>
+        <v>573214</v>
       </c>
       <c r="R7" t="n">
-        <v>6418382</v>
+        <v>6418328</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,7 +1332,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15280-2025 artfynd.xlsx
+++ b/artfynd/A 15280-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123737248</v>
+        <v>123737290</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573300</v>
+        <v>573157</v>
       </c>
       <c r="R2" t="n">
-        <v>6418290</v>
+        <v>6418382</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,6 +771,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123737290</v>
+        <v>123737422</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,32 +802,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -841,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573157</v>
+        <v>573334</v>
       </c>
       <c r="R3" t="n">
-        <v>6418382</v>
+        <v>6418407</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123737422</v>
+        <v>123737248</v>
       </c>
       <c r="B4" t="n">
-        <v>105095</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,31 +917,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573334</v>
+        <v>573300</v>
       </c>
       <c r="R4" t="n">
-        <v>6418407</v>
+        <v>6418290</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,7 +997,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123737360</v>
+        <v>123737397</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>95683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,49 +1027,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 15280, Stenserum, Sm</t>
+          <t>A 15280. Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573186</v>
+        <v>573206</v>
       </c>
       <c r="R5" t="n">
-        <v>6418398</v>
+        <v>6418383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123737397</v>
+        <v>123737360</v>
       </c>
       <c r="B6" t="n">
-        <v>95683</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1141,42 +1134,49 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 15280. Stenserum, Sm</t>
+          <t>A 15280, Stenserum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573206</v>
+        <v>573186</v>
       </c>
       <c r="R6" t="n">
-        <v>6418383</v>
+        <v>6418398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
